--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_362_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_362_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7985</v>
+        <v>6.1769</v>
       </c>
       <c r="E2" t="n">
-        <v>4.723</v>
+        <v>5.2694</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0755</v>
+        <v>0.9075</v>
       </c>
       <c r="G2" t="n">
         <v>5.6378</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4424</v>
+        <v>-0.0639</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6642</v>
+        <v>-0.1177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2219</v>
+        <v>0.0538</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7886</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0338</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6741</v>
+        <v>0.2023</v>
       </c>
       <c r="F3" t="n">
         <v>0.3598</v>
@@ -688,10 +688,10 @@
         <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="T3" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5111</v>
+        <v>-0.1969</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9272</v>
+        <v>-1.2106</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4162</v>
+        <v>1.0137</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.7655</v>
+        <v>-1.1335</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2259</v>
+        <v>0.0276</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.5397</v>
+        <v>-1.1611</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.8569</v>
+        <v>0.922</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2645</v>
+        <v>1.1329</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5924</v>
+        <v>-0.2109</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9086</v>
+        <v>-2.0555</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0387</v>
+        <v>-1.1053</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9473</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0947</v>
+        <v>-0.744</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0895</v>
+        <v>-0.5658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0053</v>
+        <v>-0.1781</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5924</v>
+        <v>-0.4408</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2538</v>
+        <v>-0.1358</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3386</v>
+        <v>-0.305</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2229</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5988</v>
+        <v>-0.4472</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9304</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6393</v>
+        <v>-0.5767</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1457</v>
+        <v>0.0266</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5064</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9391</v>
+        <v>-1.4663</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6437</v>
+        <v>-0.767</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5827</v>
+        <v>-0.6993</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5027</v>
+        <v>0.1208</v>
       </c>
       <c r="K6" t="n">
-        <v>0.605</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1077</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4364</v>
+        <v>-1.5871</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0387</v>
+        <v>-0.851</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4751</v>
+        <v>-0.7361</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1195</v>
+        <v>-0.0382</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2513</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3708</v>
+        <v>0.056</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.6841</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3273</v>
+        <v>-1.9216</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6369</v>
+        <v>1.2376</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4663</v>
+        <v>-0.9391</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.767</v>
+        <v>0.6437</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6993</v>
+        <v>-1.5827</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1208</v>
+        <v>-0.5027</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>-1.1077</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5871</v>
+        <v>-0.4364</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.851</v>
+        <v>0.0387</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7361</v>
+        <v>-0.4751</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4257</v>
+        <v>0.0747</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>-0.0272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>0.1019</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0533</v>
+        <v>-0.7379</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8318</v>
+        <v>-0.8379</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7785</v>
+        <v>0.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1335</v>
+        <v>-2.3202</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0276</v>
+        <v>-1.2328</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1611</v>
+        <v>-1.0874</v>
       </c>
       <c r="J8" t="n">
-        <v>0.922</v>
+        <v>-1.5589</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1329</v>
+        <v>-1.4719</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2109</v>
+        <v>-0.0871</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0555</v>
+        <v>-0.7613</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1053</v>
+        <v>0.2391</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.0004</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2473</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6004</v>
+        <v>0.6546</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.187</v>
+        <v>0.1849</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4134</v>
+        <v>0.4696</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3186</v>
+        <v>-0.9275</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6203</v>
+        <v>-1.4109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3016</v>
+        <v>0.4834</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3202</v>
+        <v>-4.7655</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2328</v>
+        <v>-2.2259</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0874</v>
+        <v>-2.5397</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5589</v>
+        <v>-2.8569</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4719</v>
+        <v>-2.2645</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0871</v>
+        <v>-0.5924</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7613</v>
+        <v>-1.9086</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2391</v>
+        <v>0.0387</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0004</v>
+        <v>-1.9473</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0738</v>
+        <v>0.6783</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>0.6058</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6713</v>
+        <v>0.0725</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3819</v>
+        <v>-1.7619</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9562</v>
+        <v>-2.5453</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4257</v>
+        <v>0.7834</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3427</v>
+        <v>-1.7579</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8247</v>
+        <v>0.3602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.482</v>
+        <v>-2.1181</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0729</v>
+        <v>-1.6293</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1329</v>
+        <v>0.0672</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.6965</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7302</v>
+        <v>-0.1286</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3082</v>
+        <v>0.293</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.422</v>
+        <v>-0.4216</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7598</v>
+        <v>-0.004</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4708</v>
+        <v>0.2438</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2891</v>
+        <v>-0.2478</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8608</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1322</v>
+        <v>-2.0508</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7812</v>
+        <v>-1.5578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.649</v>
+        <v>-0.4929</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7579</v>
+        <v>0.3427</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3602</v>
+        <v>0.8247</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1181</v>
+        <v>-0.482</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6293</v>
+        <v>2.0729</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0672</v>
+        <v>1.1329</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6965</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1286</v>
+        <v>-1.7302</v>
       </c>
       <c r="N11" t="n">
-        <v>0.293</v>
+        <v>-0.3082</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4216</v>
+        <v>-1.422</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3743</v>
+        <v>1.091</v>
       </c>
       <c r="T11" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.8691</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3822</v>
+        <v>0.2219</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8608</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1214</v>
+        <v>-3.1243</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6955</v>
+        <v>-3.8999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.574</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4602</v>
@@ -1390,13 +1390,13 @@
         <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2486</v>
+        <v>0.2458</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1537</v>
+        <v>-0.0507</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0949</v>
+        <v>0.2965</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8821</v>
+        <v>-3.762</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.1419</v>
+        <v>-8.021500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.259799999999999</v>
+        <v>4.2599</v>
       </c>
       <c r="G13" t="n">
         <v>-10.3841</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9480999999999999</v>
+        <v>-0.9481000000000002</v>
       </c>
       <c r="I13" t="n">
         <v>-9.436199999999999</v>
@@ -1447,7 +1447,7 @@
         <v>1.6488</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04899999999999971</v>
+        <v>0.04900000000000015</v>
       </c>
       <c r="M13" t="n">
         <v>-12.082</v>
@@ -1468,19 +1468,19 @@
         <v>19.716</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4917999999999999</v>
+        <v>1.6123</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3120000000000002</v>
+        <v>0.8084000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8041000000000001</v>
+        <v>0.8039000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7886000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>3.389500000000001</v>
+        <v>3.3895</v>
       </c>
       <c r="X13" t="n">
         <v>-4.178100000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3326</v>
+        <v>4.7265</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7206</v>
+        <v>2.1924</v>
       </c>
       <c r="F14" t="n">
-        <v>2.612</v>
+        <v>2.534</v>
       </c>
       <c r="G14" t="n">
         <v>4.859</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4362</v>
+        <v>-0.0424</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3853</v>
+        <v>0.3073</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9911</v>
+        <v>3.2657</v>
       </c>
       <c r="E15" t="n">
-        <v>2.633</v>
+        <v>2.515</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3581</v>
+        <v>0.7507</v>
       </c>
       <c r="G15" t="n">
         <v>2.909</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.3567</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4955</v>
+        <v>0.3776</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4134</v>
+        <v>-0.0209</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6422</v>
+        <v>2.9352</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.22</v>
+        <v>0.2518</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8622</v>
+        <v>2.6834</v>
       </c>
       <c r="G16" t="n">
         <v>3.9578</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.326</v>
+        <v>0.619</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6915</v>
+        <v>0.5127</v>
       </c>
       <c r="V16" t="n">
         <v>0.6778999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1567</v>
+        <v>1.3361</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0147</v>
+        <v>-1.1648</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1421</v>
+        <v>2.501</v>
       </c>
       <c r="G17" t="n">
         <v>1.3877</v>
@@ -1780,13 +1780,13 @@
         <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.854</v>
+        <v>0.0334</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1641</v>
+        <v>-0.0154</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3101</v>
+        <v>0.0488</v>
       </c>
       <c r="V17" t="n">
         <v>2.0026</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2416</v>
+        <v>1.1401</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4356</v>
+        <v>-0.6715</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6772</v>
+        <v>1.8116</v>
       </c>
       <c r="G18" t="n">
         <v>0.0511</v>
@@ -1858,13 +1858,13 @@
         <v>2.5515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2012</v>
+        <v>-0.3027</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0167</v>
+        <v>0.1177</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9883</v>
+        <v>0.4328</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6759</v>
+        <v>1.3221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6876</v>
+        <v>-0.8892</v>
       </c>
       <c r="G19" t="n">
         <v>0.7286</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0597</v>
+        <v>-0.6152</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0993</v>
+        <v>-0.3009</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8603</v>
+        <v>0.0424</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0229</v>
+        <v>-1.8418</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8373</v>
+        <v>1.8843</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8534</v>
+        <v>-0.7313</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3913</v>
+        <v>-1.521</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2447</v>
+        <v>0.7897</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4434</v>
+        <v>-2.1646</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3025</v>
+        <v>-2.275</v>
       </c>
       <c r="L20" t="n">
-        <v>1.141</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.59</v>
+        <v>1.4333</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6938</v>
+        <v>0.754</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>0.6793</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.322</v>
+        <v>0.4</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>0.181</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2473</v>
+        <v>0.219</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9563</v>
+        <v>-0.7594</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3136</v>
+        <v>-0.0229</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3573</v>
+        <v>-0.7365</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7313</v>
+        <v>0.8534</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.521</v>
+        <v>-0.3913</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7897</v>
+        <v>1.2447</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1646</v>
+        <v>1.4434</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.275</v>
+        <v>0.3025</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1104</v>
+        <v>1.141</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4333</v>
+        <v>-0.59</v>
       </c>
       <c r="N21" t="n">
-        <v>0.754</v>
+        <v>-0.6938</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6793</v>
+        <v>0.1038</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5988</v>
+        <v>-0.2212</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2908</v>
+        <v>-0.0747</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3079</v>
+        <v>-0.1465</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.679</v>
+        <v>-2.2009</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6352</v>
+        <v>-0.989</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0439</v>
+        <v>-1.2119</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3451</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0398</v>
+        <v>0.5179</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7196</v>
+        <v>0.3657</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6892</v>
+        <v>-2.3518</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2551</v>
+        <v>-4.7833</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5659</v>
+        <v>2.4315</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0758</v>
@@ -2248,13 +2248,13 @@
         <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6519</v>
+        <v>-0.3145</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1202</v>
+        <v>-0.6484</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4683</v>
+        <v>0.3339</v>
       </c>
       <c r="V23" t="n">
         <v>0.6468</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2858</v>
+        <v>-2.8983</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9576</v>
+        <v>-1.6037</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3282</v>
+        <v>-1.2946</v>
       </c>
       <c r="G24" t="n">
         <v>0.7897999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5241</v>
+        <v>-0.1366</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3655</v>
+        <v>-0.0116</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1586</v>
+        <v>-0.125</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.8819</v>
+        <v>5.668400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7958</v>
+        <v>-4.7957</v>
       </c>
       <c r="F25" t="n">
-        <v>9.6778</v>
+        <v>10.4643</v>
       </c>
       <c r="G25" t="n">
         <v>10.3842</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4920000000000002</v>
+        <v>0.2944000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.804</v>
+        <v>-0.8039000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3120999999999999</v>
+        <v>1.0983</v>
       </c>
       <c r="V25" t="n">
         <v>0.7886000000000002</v>
